--- a/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T12:43:17+00:00</t>
+    <t>2025-02-28T12:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T12:55:38+00:00</t>
+    <t>2025-03-03T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T10:30:12+00:00</t>
+    <t>2025-03-03T10:32:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T10:32:17+00:00</t>
+    <t>2025-03-03T13:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T13:20:06+00:00</t>
+    <t>2025-03-06T13:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev1/StructureDefinition-FunctionalStatus-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T13:48:27+00:00</t>
+    <t>2025-03-06T17:13:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
